--- a/marketing_forms/003_marketing_service_order_form--marketing_forms.xlsx
+++ b/marketing_forms/003_marketing_service_order_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_1</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marketing_service_order</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +547,76 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_2</t>
+          <t>project_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marketing_service_order_details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the project about?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter project details</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_3</t>
+          <t>project_start_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marketing_service_order_review</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>When is the project start date?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter project start date</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_4</t>
+          <t>project_deadline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marketing_service_order_summary</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>When is the project deadline?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter project deadline</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_5</t>
+          <t>project_lead_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_details</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Project Lead Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter project lead name</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +655,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_6</t>
+          <t>project_lead_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>marketing_service_order_notes</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your email?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter email</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_start_date</t>
+          <t>project_lead_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_start_date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your phone?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter phone</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_7</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your project status?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select status</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_8</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter comments</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +763,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_9</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_notes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter notes</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>project_status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter review</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,38 +817,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_12</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter summary</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_start_date</t>
+          <t>project_lead_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>project_start_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Lead 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter project lead name</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_deadline</t>
+          <t>project_lead_2_email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>project_deadline</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Email 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter email</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_lead</t>
+          <t>project_lead_2_phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>project_lead</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Phone 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter phone</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_lead_phone</t>
+          <t>project_lead_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>project_lead_phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Lead 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter project lead name</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_17</t>
+          <t>project_lead_3_email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Email 3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter email</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,177 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_page_18</t>
+          <t>project_lead_3_phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>marketing_service_order_form_notes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Phone 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter phone</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_lead_email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>project_lead_email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_start_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>project_start_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>project_deadline</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>project_deadline</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>marketing_service_order_form_notes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1154,23 +1065,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>paused</t>
         </is>
       </c>
     </row>
